--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65374_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65374_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd3b151db9ad94e3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf3672887d2074102"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7642</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65374_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_65374_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf3672887d2074102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbe6ffc12031c49cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6529</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7029</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6513</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7463</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7708</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7842</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7708</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7479</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6992</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6535</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6692</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7375</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7658</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
